--- a/Reports/Tribunal/PenaltyCalculate/PenaltyCalculate.xlsx
+++ b/Reports/Tribunal/PenaltyCalculate/PenaltyCalculate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\Tribunal\PenaltyCalculate\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF7163D-1846-40D2-9F4F-F9B04EFFE131}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110"/>
+    <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$D$7:$H$12</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -99,9 +105,6 @@
     <t>Сумма долга</t>
   </si>
   <si>
-    <t xml:space="preserve"> " = ".number_format($t1['total'], 2, ',', ' ')." Х ".number_format($t1['days'], 0, ',', ' ')." Х ".$t1['del_txt']." Х ".number_format($t1['rate'], 0, ',', ' ')."%"</t>
-  </si>
-  <si>
     <t>$t1['del_txt']</t>
   </si>
   <si>
@@ -169,16 +172,19 @@
   </si>
   <si>
     <t>"Представитель ".$this-&gt;H['name_organization']." (по доверенности)  __________________".$this-&gt;H['Signatory']</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> " = ".number_format($t1['total'], 2, ',', ' ')." Х ".number_format($t1['days'], 0, ',', ' ')." Х ".$t1['del_txt']." Х ".number_format($t1['rate'], 2, ',', ' ')."%"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
@@ -496,10 +502,10 @@
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 3" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="2"/>
-    <cellStyle name="Обычный 5" xfId="3"/>
-    <cellStyle name="Обычный 6" xfId="4"/>
+    <cellStyle name="Обычный 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 6" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -508,6 +514,14 @@
       <color rgb="FFFCFCD2"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -554,7 +568,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -586,9 +600,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -620,6 +652,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -795,12 +845,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" customWidth="1"/>
     <col min="2" max="3" width="12.85546875" style="1" customWidth="1"/>
@@ -815,7 +865,7 @@
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.75">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A1" s="36"/>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -841,9 +891,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.75">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -854,9 +904,9 @@
       <c r="H2" s="37"/>
       <c r="I2" s="18"/>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -875,9 +925,9 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I4" s="26"/>
       <c r="J4" s="1"/>
@@ -889,18 +939,18 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -911,7 +961,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I6" s="26"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -922,7 +972,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
     </row>
-    <row r="7" spans="1:20" ht="20.25" customHeight="1">
+    <row r="7" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27"/>
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
@@ -941,7 +991,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:20" ht="18.95" customHeight="1">
+    <row r="8" spans="1:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="41" t="s">
         <v>25</v>
       </c>
@@ -964,7 +1014,7 @@
       </c>
       <c r="I8" s="20"/>
     </row>
-    <row r="9" spans="1:20" ht="18.95" customHeight="1">
+    <row r="9" spans="1:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="41"/>
       <c r="B9" s="10" t="s">
         <v>12</v>
@@ -987,7 +1037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="4.5" customHeight="1">
+    <row r="10" spans="1:20" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50"/>
       <c r="B10" s="51"/>
       <c r="C10" s="51"/>
@@ -1001,20 +1051,20 @@
         <v>5</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M10" s="7">
         <v>2</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
     </row>
-    <row r="11" spans="1:20" ht="38.1" customHeight="1">
+    <row r="11" spans="1:20" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
@@ -1024,7 +1074,7 @@
       <c r="G11" s="48"/>
       <c r="H11" s="49"/>
       <c r="I11" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1033,15 +1083,15 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:20" ht="18.95" customHeight="1">
+    <row r="12" spans="1:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>22</v>
@@ -1050,16 +1100,16 @@
         <v>23</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>5</v>
@@ -1076,9 +1126,9 @@
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
     </row>
-    <row r="13" spans="1:20" ht="12" customHeight="1">
+    <row r="13" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="45"/>
       <c r="C13" s="45"/>
@@ -1097,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>4</v>
@@ -1106,9 +1156,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="18" customHeight="1">
+    <row r="14" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -1117,7 +1167,7 @@
       <c r="F14" s="34"/>
       <c r="G14" s="35"/>
       <c r="H14" s="25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I14" s="22"/>
       <c r="K14" s="9" t="s">
@@ -1148,9 +1198,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="43.5" customHeight="1">
+    <row r="15" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
@@ -1159,7 +1209,7 @@
       <c r="F15" s="31"/>
       <c r="G15" s="32"/>
       <c r="H15" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>9</v>
@@ -1171,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>10</v>
@@ -1183,18 +1233,18 @@
         <v>8</v>
       </c>
       <c r="S15" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T15" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="K16" s="3" t="s">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M16" s="4">
         <v>5</v>
@@ -1203,17 +1253,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="O20" s="6" t="s">
         <v>4</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1241,9 +1291,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1252,9 +1302,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
